--- a/app/Console/Commands/Course/PRF_Courses.xlsx
+++ b/app/Console/Commands/Course/PRF_Courses.xlsx
@@ -177,7 +177,7 @@
     <t>TIME MANAGEMENT</t>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
+    <t>Effective time management is essential for missioners to maximize productivity and ensure the success of PRF missions.</t>
   </si>
   <si>
     <t>Reporting to a Mission</t>
